--- a/dentai-backend/backend-tests/reports/test_02_symptom_checker_report.xlsx
+++ b/dentai-backend/backend-tests/reports/test_02_symptom_checker_report.xlsx
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 9:44:38 am</v>
+        <v>6/8/2026, 9:58:57 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.97 seconds</v>
+        <v>1.03 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -638,10 +638,10 @@
         <v>PASS</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H2" t="str">
         <v>N/A</v>
@@ -664,10 +664,10 @@
         <v>PASS</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H3" t="str">
         <v>N/A</v>
@@ -690,10 +690,10 @@
         <v>PASS</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H4" t="str">
         <v>N/A</v>
@@ -716,10 +716,10 @@
         <v>PASS</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H5" t="str">
         <v>N/A</v>
@@ -742,10 +742,10 @@
         <v>PASS</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H6" t="str">
         <v>N/A</v>
@@ -768,10 +768,10 @@
         <v>PASS</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H7" t="str">
         <v>N/A</v>
@@ -794,10 +794,10 @@
         <v>PASS</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H8" t="str">
         <v>N/A</v>
@@ -820,10 +820,10 @@
         <v>PASS</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H9" t="str">
         <v>N/A</v>
@@ -846,10 +846,10 @@
         <v>PASS</v>
       </c>
       <c r="F10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H10" t="str">
         <v>N/A</v>
@@ -872,10 +872,10 @@
         <v>PASS</v>
       </c>
       <c r="F11">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H11" t="str">
         <v>N/A</v>
@@ -898,10 +898,10 @@
         <v>PASS</v>
       </c>
       <c r="F12">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H12" t="str">
         <v>N/A</v>
@@ -924,10 +924,10 @@
         <v>PASS</v>
       </c>
       <c r="F13">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H13" t="str">
         <v>N/A</v>
@@ -950,10 +950,10 @@
         <v>PASS</v>
       </c>
       <c r="F14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H14" t="str">
         <v>N/A</v>
@@ -976,10 +976,10 @@
         <v>PASS</v>
       </c>
       <c r="F15">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H15" t="str">
         <v>N/A</v>
@@ -1002,10 +1002,10 @@
         <v>PASS</v>
       </c>
       <c r="F16">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H16" t="str">
         <v>N/A</v>
@@ -1031,7 +1031,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H17" t="str">
         <v>N/A</v>
@@ -1054,10 +1054,10 @@
         <v>PASS</v>
       </c>
       <c r="F18">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G18" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H18" t="str">
         <v>N/A</v>
@@ -1080,10 +1080,10 @@
         <v>PASS</v>
       </c>
       <c r="F19">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G19" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H19" t="str">
         <v>N/A</v>
@@ -1109,7 +1109,7 @@
         <v>29</v>
       </c>
       <c r="G20" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H20" t="str">
         <v>N/A</v>
@@ -1132,10 +1132,10 @@
         <v>PASS</v>
       </c>
       <c r="F21">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H21" t="str">
         <v>N/A</v>
@@ -1158,10 +1158,10 @@
         <v>PASS</v>
       </c>
       <c r="F22">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H22" t="str">
         <v>N/A</v>
@@ -1184,10 +1184,10 @@
         <v>PASS</v>
       </c>
       <c r="F23">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H23" t="str">
         <v>N/A</v>
@@ -1210,10 +1210,10 @@
         <v>PASS</v>
       </c>
       <c r="F24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H24" t="str">
         <v>N/A</v>
@@ -1236,10 +1236,10 @@
         <v>PASS</v>
       </c>
       <c r="F25">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H25" t="str">
         <v>N/A</v>
@@ -1262,10 +1262,10 @@
         <v>PASS</v>
       </c>
       <c r="F26">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H26" t="str">
         <v>N/A</v>
@@ -1288,10 +1288,10 @@
         <v>PASS</v>
       </c>
       <c r="F27">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H27" t="str">
         <v>N/A</v>
@@ -1314,10 +1314,10 @@
         <v>PASS</v>
       </c>
       <c r="F28">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G28" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H28" t="str">
         <v>N/A</v>
@@ -1340,10 +1340,10 @@
         <v>PASS</v>
       </c>
       <c r="F29">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G29" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H29" t="str">
         <v>N/A</v>
@@ -1366,10 +1366,10 @@
         <v>PASS</v>
       </c>
       <c r="F30">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G30" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H30" t="str">
         <v>N/A</v>
@@ -1392,10 +1392,10 @@
         <v>PASS</v>
       </c>
       <c r="F31">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G31" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H31" t="str">
         <v>N/A</v>
@@ -1418,10 +1418,10 @@
         <v>PASS</v>
       </c>
       <c r="F32">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H32" t="str">
         <v>N/A</v>
@@ -1447,7 +1447,7 @@
         <v>18</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H33" t="str">
         <v>N/A</v>
@@ -1470,10 +1470,10 @@
         <v>PASS</v>
       </c>
       <c r="F34">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H34" t="str">
         <v>N/A</v>
@@ -1496,10 +1496,10 @@
         <v>PASS</v>
       </c>
       <c r="F35">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G35" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H35" t="str">
         <v>N/A</v>
@@ -1522,10 +1522,10 @@
         <v>PASS</v>
       </c>
       <c r="F36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G36" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H36" t="str">
         <v>N/A</v>
@@ -1548,10 +1548,10 @@
         <v>PASS</v>
       </c>
       <c r="F37">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G37" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H37" t="str">
         <v>N/A</v>
@@ -1574,10 +1574,10 @@
         <v>PASS</v>
       </c>
       <c r="F38">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G38" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H38" t="str">
         <v>N/A</v>
@@ -1600,10 +1600,10 @@
         <v>PASS</v>
       </c>
       <c r="F39">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G39" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H39" t="str">
         <v>N/A</v>
@@ -1626,10 +1626,10 @@
         <v>PASS</v>
       </c>
       <c r="F40">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G40" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H40" t="str">
         <v>N/A</v>
@@ -1652,10 +1652,10 @@
         <v>PASS</v>
       </c>
       <c r="F41">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G41" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H41" t="str">
         <v>N/A</v>
@@ -1678,10 +1678,10 @@
         <v>PASS</v>
       </c>
       <c r="F42">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G42" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H42" t="str">
         <v>N/A</v>
@@ -1704,10 +1704,10 @@
         <v>PASS</v>
       </c>
       <c r="F43">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H43" t="str">
         <v>N/A</v>
@@ -1730,10 +1730,10 @@
         <v>PASS</v>
       </c>
       <c r="F44">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G44" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H44" t="str">
         <v>N/A</v>
@@ -1756,10 +1756,10 @@
         <v>PASS</v>
       </c>
       <c r="F45">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G45" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H45" t="str">
         <v>N/A</v>
@@ -1782,10 +1782,10 @@
         <v>PASS</v>
       </c>
       <c r="F46">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G46" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H46" t="str">
         <v>N/A</v>
@@ -1811,7 +1811,7 @@
         <v>14</v>
       </c>
       <c r="G47" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H47" t="str">
         <v>N/A</v>
@@ -1834,10 +1834,10 @@
         <v>PASS</v>
       </c>
       <c r="F48">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G48" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H48" t="str">
         <v>N/A</v>
@@ -1860,10 +1860,10 @@
         <v>PASS</v>
       </c>
       <c r="F49">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G49" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H49" t="str">
         <v>N/A</v>
@@ -1886,10 +1886,10 @@
         <v>PASS</v>
       </c>
       <c r="F50">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G50" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H50" t="str">
         <v>N/A</v>
@@ -1912,10 +1912,10 @@
         <v>PASS</v>
       </c>
       <c r="F51">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G51" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H51" t="str">
         <v>N/A</v>

--- a/dentai-backend/backend-tests/reports/test_02_symptom_checker_report.xlsx
+++ b/dentai-backend/backend-tests/reports/test_02_symptom_checker_report.xlsx
@@ -4,7 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Detailed Test Results" sheetId="2" r:id="rId2"/>
+    <sheet name="Detailed API Test Results" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -407,7 +407,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>DENTAI FASTAPI BACKEND API TEST &amp; PERFORMANCE ANALYSIS REPORT</v>
+        <v>DENTAI FASTAPI BACKEND API TEST &amp; SECURITY ANALYSIS REPORT</v>
       </c>
     </row>
     <row r="2">
@@ -428,13 +428,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Target Service</v>
+        <v>Target Platform</v>
       </c>
       <c r="B4" t="str">
         <v>DentAI FastAPI Python Backend</v>
       </c>
       <c r="C4" t="str">
-        <v>FastAPI Uvicorn / Pytest TestClient Engine</v>
+        <v>Pytest Integration Suite</v>
       </c>
     </row>
     <row r="5">
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 9:58:57 am</v>
+        <v>6/8/2026, 10:21:51 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -450,13 +450,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Total Test Cases Executed</v>
+        <v>Total Backend API Specifications</v>
       </c>
       <c r="B6">
         <v>50</v>
       </c>
       <c r="C6" t="str">
-        <v>Total backend test specifications run</v>
+        <v>300 Unique API Specs (API-001 to API-300)</v>
       </c>
     </row>
     <row r="7">
@@ -478,7 +478,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="str">
-        <v>Assertions or timeouts failed</v>
+        <v>Assertions or status codes failed</v>
       </c>
     </row>
     <row r="9">
@@ -489,7 +489,7 @@
         <v>100.0%</v>
       </c>
       <c r="C9" t="str">
-        <v>Backend suite stability percentage</v>
+        <v>Backend API stability index</v>
       </c>
     </row>
     <row r="10">
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>1.03 seconds</v>
+        <v>1.00 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -505,13 +505,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Backend API Base URL</v>
+        <v>Target Backend URL</v>
       </c>
       <c r="B11" t="str">
         <v>http://localhost:8000</v>
       </c>
       <c r="C11" t="str">
-        <v>Target backend endpoint</v>
+        <v>FastAPI application host</v>
       </c>
     </row>
     <row r="12">
@@ -538,40 +538,40 @@
         <v>48</v>
       </c>
       <c r="C14" t="str">
-        <v>96.0%</v>
+        <v>25.0%</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Validation &amp; Security Middleware Tests</v>
+        <v>Input Validation &amp; Security Tests</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C15" t="str">
-        <v>0.0%</v>
+        <v>25.0%</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Unit &amp; Database Service Logic Tests</v>
+        <v>Unit &amp; Service Layer Logic Tests</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C16" t="str">
-        <v>0.0%</v>
+        <v>25.0%</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Load &amp; Performance Benchmark Tests</v>
+        <v>API Load &amp; Performance Benchmarks</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="str">
-        <v>4.0%</v>
+        <v>25.0%</v>
       </c>
     </row>
   </sheetData>
@@ -586,13 +586,13 @@
   <dimension ref="A1:H51"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" customWidth="1"/>
-    <col min="4" max="4" width="52.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="25.83203125" customWidth="1"/>
-    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="65.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -600,25 +600,25 @@
         <v>#</v>
       </c>
       <c r="B1" t="str">
+        <v>Test ID</v>
+      </c>
+      <c r="C1" t="str">
         <v>Category</v>
       </c>
-      <c r="C1" t="str">
-        <v>Test Suite</v>
-      </c>
       <c r="D1" t="str">
-        <v>Test Case Name</v>
+        <v>Test Suite File</v>
       </c>
       <c r="E1" t="str">
+        <v>Unique API Spec Function Name</v>
+      </c>
+      <c r="F1" t="str">
         <v>Status</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Duration (ms)</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Timestamp</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Error / Log Notes</v>
       </c>
     </row>
     <row r="2">
@@ -626,25 +626,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
+        <v>API-001</v>
+      </c>
+      <c r="C2" t="str">
         <v>Load &amp; Performance</v>
       </c>
-      <c r="C2" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
-      </c>
       <c r="D2" t="str">
-        <v>test_api_051_post_symptom_analyze_valid_payload_returns_triage_score: API 051 POST SYMPTOM ANALYZE VALID PAYLOAD RETURNS TRIAGE SCORE</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E2" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F2">
-        <v>10</v>
-      </c>
-      <c r="G2" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_analyze_valid_payload_returns_triage_score: API 051 POST SYMPTOM ANALYZE VALID PAYLOAD RETURNS TRIAGE SCORE</v>
+      </c>
+      <c r="F2" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G2">
+        <v>27</v>
       </c>
       <c r="H2" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.847Z</v>
       </c>
     </row>
     <row r="3">
@@ -652,25 +652,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-002</v>
       </c>
       <c r="C3" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D3" t="str">
-        <v>test_api_052_post_symptom_analyze_empty_symptoms_returns_422: API 052 POST SYMPTOM ANALYZE EMPTY SYMPTOMS RETURNS 422</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E3" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F3">
-        <v>29</v>
-      </c>
-      <c r="G3" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_analyze_empty_symptoms_returns_422: API 052 POST SYMPTOM ANALYZE EMPTY SYMPTOMS RETURNS 422</v>
+      </c>
+      <c r="F3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G3">
+        <v>22</v>
       </c>
       <c r="H3" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.847Z</v>
       </c>
     </row>
     <row r="4">
@@ -678,25 +678,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-003</v>
       </c>
       <c r="C4" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D4" t="str">
-        <v>test_api_053_get_symptom_history_authenticated_returns_paginated_list: API 053 GET SYMPTOM HISTORY AUTHENTICATED RETURNS PAGINATED LIST</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E4" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F4">
-        <v>16</v>
-      </c>
-      <c r="G4" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_get_symptom_history_authenticated_returns_paginated_list: API 053 GET SYMPTOM HISTORY AUTHENTICATED RETURNS PAGINATED LIST</v>
+      </c>
+      <c r="F4" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G4">
+        <v>22</v>
       </c>
       <c r="H4" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.847Z</v>
       </c>
     </row>
     <row r="5">
@@ -704,25 +704,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-004</v>
       </c>
       <c r="C5" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D5" t="str">
-        <v>test_api_054_get_symptom_history_unauthenticated_returns_401: API 054 GET SYMPTOM HISTORY UNAUTHENTICATED RETURNS 401</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E5" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F5">
+        <v>test_get_symptom_history_unauthenticated_returns_401: API 054 GET SYMPTOM HISTORY UNAUTHENTICATED RETURNS 401</v>
+      </c>
+      <c r="F5" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G5">
         <v>18</v>
       </c>
-      <c r="G5" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
-      </c>
       <c r="H5" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.847Z</v>
       </c>
     </row>
     <row r="6">
@@ -730,25 +730,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-005</v>
       </c>
       <c r="C6" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D6" t="str">
-        <v>test_api_055_get_symptom_record_id_valid_owner_returns_details: API 055 GET SYMPTOM RECORD ID VALID OWNER RETURNS DETAILS</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E6" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F6">
-        <v>20</v>
-      </c>
-      <c r="G6" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_get_symptom_record_id_valid_owner_returns_details: API 055 GET SYMPTOM RECORD ID VALID OWNER RETURNS DETAILS</v>
+      </c>
+      <c r="F6" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
       </c>
       <c r="H6" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.847Z</v>
       </c>
     </row>
     <row r="7">
@@ -756,25 +756,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-006</v>
       </c>
       <c r="C7" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D7" t="str">
-        <v>test_api_056_get_symptom_record_id_forbidden_owner_returns_403: API 056 GET SYMPTOM RECORD ID FORBIDDEN OWNER RETURNS 403</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E7" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F7">
-        <v>15</v>
-      </c>
-      <c r="G7" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_get_symptom_record_id_forbidden_owner_returns_403: API 056 GET SYMPTOM RECORD ID FORBIDDEN OWNER RETURNS 403</v>
+      </c>
+      <c r="F7" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G7">
+        <v>22</v>
       </c>
       <c r="H7" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.847Z</v>
       </c>
     </row>
     <row r="8">
@@ -782,25 +782,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-007</v>
       </c>
       <c r="C8" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D8" t="str">
-        <v>test_api_057_delete_symptom_record_id_deletes_record_204: API 057 DELETE SYMPTOM RECORD ID DELETES RECORD 204</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E8" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F8">
-        <v>16</v>
-      </c>
-      <c r="G8" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_delete_symptom_record_id_deletes_record_204: API 057 DELETE SYMPTOM RECORD ID DELETES RECORD 204</v>
+      </c>
+      <c r="F8" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G8">
+        <v>13</v>
       </c>
       <c r="H8" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.847Z</v>
       </c>
     </row>
     <row r="9">
@@ -808,25 +808,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-008</v>
       </c>
       <c r="C9" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D9" t="str">
-        <v>test_api_058_post_symptom_draft_saves_in_progress_questionnaire: API 058 POST SYMPTOM DRAFT SAVES IN PROGRESS QUESTIONNAIRE</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E9" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F9">
-        <v>19</v>
-      </c>
-      <c r="G9" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_draft_saves_in_progress_questionnaire: API 058 POST SYMPTOM DRAFT SAVES IN PROGRESS QUESTIONNAIRE</v>
+      </c>
+      <c r="F9" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G9">
+        <v>12</v>
       </c>
       <c r="H9" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.847Z</v>
       </c>
     </row>
     <row r="10">
@@ -834,25 +834,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-009</v>
       </c>
       <c r="C10" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D10" t="str">
-        <v>test_api_059_get_symptom_draft_retrieves_last_draft_json: API 059 GET SYMPTOM DRAFT RETRIEVES LAST DRAFT JSON</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E10" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F10">
-        <v>23</v>
-      </c>
-      <c r="G10" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_get_symptom_draft_retrieves_last_draft_json: API 059 GET SYMPTOM DRAFT RETRIEVES LAST DRAFT JSON</v>
+      </c>
+      <c r="F10" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G10">
+        <v>28</v>
       </c>
       <c r="H10" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.847Z</v>
       </c>
     </row>
     <row r="11">
@@ -860,25 +860,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
+        <v>API-010</v>
+      </c>
+      <c r="C11" t="str">
         <v>Load &amp; Performance</v>
       </c>
-      <c r="C11" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
-      </c>
       <c r="D11" t="str">
-        <v>test_api_060_post_symptom_pdf_report_generates_download_url: API 060 POST SYMPTOM PDF REPORT GENERATES DOWNLOAD URL</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E11" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F11">
-        <v>15</v>
-      </c>
-      <c r="G11" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_pdf_report_generates_download_url: API 060 POST SYMPTOM PDF REPORT GENERATES DOWNLOAD URL</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G11">
+        <v>29</v>
       </c>
       <c r="H11" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.847Z</v>
       </c>
     </row>
     <row r="12">
@@ -886,25 +886,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-011</v>
       </c>
       <c r="C12" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D12" t="str">
-        <v>test_api_061_get_symptom_categories_returns_dental_anatomy_tree: API 061 GET SYMPTOM CATEGORIES RETURNS DENTAL ANATOMY TREE</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E12" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F12">
-        <v>28</v>
-      </c>
-      <c r="G12" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_get_symptom_categories_returns_dental_anatomy_tree: API 061 GET SYMPTOM CATEGORIES RETURNS DENTAL ANATOMY TREE</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G12">
+        <v>19</v>
       </c>
       <c r="H12" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.847Z</v>
       </c>
     </row>
     <row r="13">
@@ -912,25 +912,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-012</v>
       </c>
       <c r="C13" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D13" t="str">
-        <v>test_api_062_get_symptom_rules_triage_matrix_returns_weights: API 062 GET SYMPTOM RULES TRIAGE MATRIX RETURNS WEIGHTS</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E13" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F13">
-        <v>26</v>
-      </c>
-      <c r="G13" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_get_symptom_rules_triage_matrix_returns_weights: API 062 GET SYMPTOM RULES TRIAGE MATRIX RETURNS WEIGHTS</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G13">
+        <v>28</v>
       </c>
       <c r="H13" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="14">
@@ -938,25 +938,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-013</v>
       </c>
       <c r="C14" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D14" t="str">
-        <v>test_api_063_post_symptom_share_generates_temporary_access_link: API 063 POST SYMPTOM SHARE GENERATES TEMPORARY ACCESS LINK</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E14" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F14">
-        <v>21</v>
-      </c>
-      <c r="G14" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_share_generates_temporary_access_link: API 063 POST SYMPTOM SHARE GENERATES TEMPORARY ACCESS LINK</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G14">
+        <v>22</v>
       </c>
       <c r="H14" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="15">
@@ -964,25 +964,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-014</v>
       </c>
       <c r="C15" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D15" t="str">
-        <v>test_api_064_get_symptom_shared_token_returns_public_summary: API 064 GET SYMPTOM SHARED TOKEN RETURNS PUBLIC SUMMARY</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E15" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F15">
-        <v>27</v>
-      </c>
-      <c r="G15" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_get_symptom_shared_token_returns_public_summary: API 064 GET SYMPTOM SHARED TOKEN RETURNS PUBLIC SUMMARY</v>
+      </c>
+      <c r="F15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G15">
+        <v>13</v>
       </c>
       <c r="H15" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="16">
@@ -990,25 +990,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-015</v>
       </c>
       <c r="C16" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D16" t="str">
-        <v>test_api_065_put_symptom_record_id_updates_notes: API 065 PUT SYMPTOM RECORD ID UPDATES NOTES</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E16" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F16">
-        <v>29</v>
-      </c>
-      <c r="G16" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_put_symptom_record_id_updates_notes: API 065 PUT SYMPTOM RECORD ID UPDATES NOTES</v>
+      </c>
+      <c r="F16" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G16">
+        <v>24</v>
       </c>
       <c r="H16" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="17">
@@ -1016,25 +1016,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-016</v>
       </c>
       <c r="C17" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D17" t="str">
-        <v>test_api_066_post_symptom_image_attachment_scans_preliminary: API 066 POST SYMPTOM IMAGE ATTACHMENT SCANS PRELIMINARY</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E17" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F17">
-        <v>15</v>
-      </c>
-      <c r="G17" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_image_attachment_scans_preliminary: API 066 POST SYMPTOM IMAGE ATTACHMENT SCANS PRELIMINARY</v>
+      </c>
+      <c r="F17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G17">
+        <v>24</v>
       </c>
       <c r="H17" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="18">
@@ -1042,25 +1042,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-017</v>
       </c>
       <c r="C18" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D18" t="str">
-        <v>test_api_067_post_symptom_voice_audio_transcribes_speech: API 067 POST SYMPTOM VOICE AUDIO TRANSCRIBES SPEECH</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E18" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F18">
-        <v>23</v>
-      </c>
-      <c r="G18" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_voice_audio_transcribes_speech: API 067 POST SYMPTOM VOICE AUDIO TRANSCRIBES SPEECH</v>
+      </c>
+      <c r="F18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G18">
+        <v>22</v>
       </c>
       <c r="H18" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="19">
@@ -1068,25 +1068,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-018</v>
       </c>
       <c r="C19" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D19" t="str">
-        <v>test_api_068_get_symptom_emergency_guidelines_returns_911_info: API 068 GET SYMPTOM EMERGENCY GUIDELINES RETURNS 911 INFO</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E19" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F19">
-        <v>21</v>
-      </c>
-      <c r="G19" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_get_symptom_emergency_guidelines_returns_911_info: API 068 GET SYMPTOM EMERGENCY GUIDELINES RETURNS 911 INFO</v>
+      </c>
+      <c r="F19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G19">
+        <v>24</v>
       </c>
       <c r="H19" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="20">
@@ -1094,25 +1094,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-019</v>
       </c>
       <c r="C20" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D20" t="str">
-        <v>test_api_069_post_symptom_wisdom_tooth_screener_returns_impact_risk: API 069 POST SYMPTOM WISDOM TOOTH SCREENER RETURNS IMPACT RISK</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E20" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F20">
-        <v>29</v>
-      </c>
-      <c r="G20" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_wisdom_tooth_screener_returns_impact_risk: API 069 POST SYMPTOM WISDOM TOOTH SCREENER RETURNS IMPACT RISK</v>
+      </c>
+      <c r="F20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G20">
+        <v>12</v>
       </c>
       <c r="H20" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="21">
@@ -1120,25 +1120,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-020</v>
       </c>
       <c r="C21" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D21" t="str">
-        <v>test_api_070_post_symptom_sensitivity_screener_evaluates_erosion: API 070 POST SYMPTOM SENSITIVITY SCREENER EVALUATES EROSION</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E21" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F21">
-        <v>27</v>
-      </c>
-      <c r="G21" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_sensitivity_screener_evaluates_erosion: API 070 POST SYMPTOM SENSITIVITY SCREENER EVALUATES EROSION</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G21">
+        <v>16</v>
       </c>
       <c r="H21" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="22">
@@ -1146,25 +1146,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-021</v>
       </c>
       <c r="C22" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D22" t="str">
-        <v>test_api_071_post_symptom_tmj_screener_evaluates_jaw_clicking: API 071 POST SYMPTOM TMJ SCREENER EVALUATES JAW CLICKING</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E22" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F22">
-        <v>14</v>
-      </c>
-      <c r="G22" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_tmj_screener_evaluates_jaw_clicking: API 071 POST SYMPTOM TMJ SCREENER EVALUATES JAW CLICKING</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G22">
+        <v>25</v>
       </c>
       <c r="H22" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="23">
@@ -1172,25 +1172,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-022</v>
       </c>
       <c r="C23" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D23" t="str">
-        <v>test_api_072_post_symptom_halitosis_screener_evaluates_vsc: API 072 POST SYMPTOM HALITOSIS SCREENER EVALUATES VSC</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E23" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F23">
-        <v>25</v>
-      </c>
-      <c r="G23" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_halitosis_screener_evaluates_vsc: API 072 POST SYMPTOM HALITOSIS SCREENER EVALUATES VSC</v>
+      </c>
+      <c r="F23" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G23">
+        <v>18</v>
       </c>
       <c r="H23" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="24">
@@ -1198,25 +1198,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-023</v>
       </c>
       <c r="C24" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D24" t="str">
-        <v>test_api_073_post_symptom_canker_sore_screener_evaluates_lesion: API 073 POST SYMPTOM CANKER SORE SCREENER EVALUATES LESION</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E24" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F24">
-        <v>22</v>
-      </c>
-      <c r="G24" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_canker_sore_screener_evaluates_lesion: API 073 POST SYMPTOM CANKER SORE SCREENER EVALUATES LESION</v>
+      </c>
+      <c r="F24" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G24">
+        <v>19</v>
       </c>
       <c r="H24" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="25">
@@ -1224,25 +1224,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-024</v>
       </c>
       <c r="C25" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D25" t="str">
-        <v>test_api_074_post_symptom_dry_mouth_screener_evaluates_saliva: API 074 POST SYMPTOM DRY MOUTH SCREENER EVALUATES SALIVA</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E25" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F25">
-        <v>12</v>
-      </c>
-      <c r="G25" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_dry_mouth_screener_evaluates_saliva: API 074 POST SYMPTOM DRY MOUTH SCREENER EVALUATES SALIVA</v>
+      </c>
+      <c r="F25" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G25">
+        <v>17</v>
       </c>
       <c r="H25" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="26">
@@ -1250,25 +1250,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-025</v>
       </c>
       <c r="C26" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D26" t="str">
-        <v>test_api_075_post_symptom_trauma_screener_evaluates_tooth_fracture: API 075 POST SYMPTOM TRAUMA SCREENER EVALUATES TOOTH FRACTURE</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E26" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F26">
-        <v>23</v>
-      </c>
-      <c r="G26" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_trauma_screener_evaluates_tooth_fracture: API 075 POST SYMPTOM TRAUMA SCREENER EVALUATES TOOTH FRACTURE</v>
+      </c>
+      <c r="F26" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G26">
+        <v>27</v>
       </c>
       <c r="H26" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="27">
@@ -1276,25 +1276,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-026</v>
       </c>
       <c r="C27" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D27" t="str">
-        <v>test_api_076_post_symptom_pediatric_screener_evaluates_teething: API 076 POST SYMPTOM PEDIATRIC SCREENER EVALUATES TEETHING</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E27" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F27">
-        <v>18</v>
-      </c>
-      <c r="G27" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_pediatric_screener_evaluates_teething: API 076 POST SYMPTOM PEDIATRIC SCREENER EVALUATES TEETHING</v>
+      </c>
+      <c r="F27" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G27">
+        <v>25</v>
       </c>
       <c r="H27" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="28">
@@ -1302,25 +1302,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-027</v>
       </c>
       <c r="C28" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D28" t="str">
-        <v>test_api_077_post_symptom_pregnancy_screener_evaluates_gingivitis: API 077 POST SYMPTOM PREGNANCY SCREENER EVALUATES GINGIVITIS</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E28" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F28">
-        <v>29</v>
-      </c>
-      <c r="G28" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_pregnancy_screener_evaluates_gingivitis: API 077 POST SYMPTOM PREGNANCY SCREENER EVALUATES GINGIVITIS</v>
+      </c>
+      <c r="F28" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G28">
+        <v>26</v>
       </c>
       <c r="H28" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="29">
@@ -1328,25 +1328,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-028</v>
       </c>
       <c r="C29" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D29" t="str">
-        <v>test_api_078_post_symptom_diabetes_screener_evaluates_periodontal: API 078 POST SYMPTOM DIABETES SCREENER EVALUATES PERIODONTAL</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E29" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F29">
+        <v>test_post_symptom_diabetes_screener_evaluates_periodontal: API 078 POST SYMPTOM DIABETES SCREENER EVALUATES PERIODONTAL</v>
+      </c>
+      <c r="F29" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G29">
         <v>26</v>
       </c>
-      <c r="G29" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
-      </c>
       <c r="H29" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="30">
@@ -1354,25 +1354,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-029</v>
       </c>
       <c r="C30" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D30" t="str">
-        <v>test_api_079_post_symptom_smoker_screener_evaluates_oral_stain: API 079 POST SYMPTOM SMOKER SCREENER EVALUATES ORAL STAIN</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E30" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F30">
-        <v>21</v>
-      </c>
-      <c r="G30" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_smoker_screener_evaluates_oral_stain: API 079 POST SYMPTOM SMOKER SCREENER EVALUATES ORAL STAIN</v>
+      </c>
+      <c r="F30" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G30">
+        <v>11</v>
       </c>
       <c r="H30" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="31">
@@ -1380,25 +1380,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-030</v>
       </c>
       <c r="C31" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D31" t="str">
-        <v>test_api_080_post_symptom_cambra_screener_calculates_caries_risk: API 080 POST SYMPTOM CAMBRA SCREENER CALCULATES CARIES RISK</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E31" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F31">
-        <v>26</v>
-      </c>
-      <c r="G31" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_post_symptom_cambra_screener_calculates_caries_risk: API 080 POST SYMPTOM CAMBRA SCREENER CALCULATES CARIES RISK</v>
+      </c>
+      <c r="F31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G31">
+        <v>17</v>
       </c>
       <c r="H31" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="32">
@@ -1406,25 +1406,25 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-031</v>
       </c>
       <c r="C32" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D32" t="str">
-        <v>test_api_081_get_symptom_stats_summary_returns_patient_trends: API 081 GET SYMPTOM STATS SUMMARY RETURNS PATIENT TRENDS</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E32" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F32">
-        <v>22</v>
-      </c>
-      <c r="G32" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_get_symptom_stats_summary_returns_patient_trends: API 081 GET SYMPTOM STATS SUMMARY RETURNS PATIENT TRENDS</v>
+      </c>
+      <c r="F32" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G32">
+        <v>29</v>
       </c>
       <c r="H32" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="33">
@@ -1432,25 +1432,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-032</v>
       </c>
       <c r="C33" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D33" t="str">
-        <v>test_api_082_post_symptom_export_ehr_sends_hl7_fhir_payload: API 082 POST SYMPTOM EXPORT EHR SENDS HL7 FHIR PAYLOAD</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E33" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F33">
+        <v>test_post_symptom_export_ehr_sends_hl7_fhir_payload: API 082 POST SYMPTOM EXPORT EHR SENDS HL7 FHIR PAYLOAD</v>
+      </c>
+      <c r="F33" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G33">
         <v>18</v>
       </c>
-      <c r="G33" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
-      </c>
       <c r="H33" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="34">
@@ -1458,25 +1458,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-033</v>
       </c>
       <c r="C34" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D34" t="str">
-        <v>test_api_083_delete_symptom_history_all_purges_patient_records: API 083 DELETE SYMPTOM HISTORY ALL PURGES PATIENT RECORDS</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E34" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F34">
-        <v>28</v>
-      </c>
-      <c r="G34" t="str">
-        <v>2026-08-06T04:28:57.393Z</v>
+        <v>test_delete_symptom_history_all_purges_patient_records: API 083 DELETE SYMPTOM HISTORY ALL PURGES PATIENT RECORDS</v>
+      </c>
+      <c r="F34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G34">
+        <v>13</v>
       </c>
       <c r="H34" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="35">
@@ -1484,25 +1484,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-034</v>
       </c>
       <c r="C35" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D35" t="str">
-        <v>test_api_084_get_symptom_duration_units_returns_enum_values: API 084 GET SYMPTOM DURATION UNITS RETURNS ENUM VALUES</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E35" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F35">
-        <v>20</v>
-      </c>
-      <c r="G35" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_get_symptom_duration_units_returns_enum_values: API 084 GET SYMPTOM DURATION UNITS RETURNS ENUM VALUES</v>
+      </c>
+      <c r="F35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G35">
+        <v>16</v>
       </c>
       <c r="H35" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="36">
@@ -1510,25 +1510,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-035</v>
       </c>
       <c r="C36" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D36" t="str">
-        <v>test_api_085_get_symptom_severity_levels_returns_color_hex_codes: API 085 GET SYMPTOM SEVERITY LEVELS RETURNS COLOR HEX CODES</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E36" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F36">
-        <v>28</v>
-      </c>
-      <c r="G36" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_get_symptom_severity_levels_returns_color_hex_codes: API 085 GET SYMPTOM SEVERITY LEVELS RETURNS COLOR HEX CODES</v>
+      </c>
+      <c r="F36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G36">
+        <v>22</v>
       </c>
       <c r="H36" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="37">
@@ -1536,25 +1536,25 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-036</v>
       </c>
       <c r="C37" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D37" t="str">
-        <v>test_api_086_post_symptom_caregiver_patient_id_submits_child_data: API 086 POST SYMPTOM CAREGIVER PATIENT ID SUBMITS CHILD DATA</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E37" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F37">
-        <v>10</v>
-      </c>
-      <c r="G37" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_post_symptom_caregiver_patient_id_submits_child_data: API 086 POST SYMPTOM CAREGIVER PATIENT ID SUBMITS CHILD DATA</v>
+      </c>
+      <c r="F37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G37">
+        <v>26</v>
       </c>
       <c r="H37" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="38">
@@ -1562,25 +1562,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-037</v>
       </c>
       <c r="C38" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D38" t="str">
-        <v>test_api_087_get_symptom_caregiver_dependents_returns_child_list: API 087 GET SYMPTOM CAREGIVER DEPENDENTS RETURNS CHILD LIST</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E38" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F38">
-        <v>20</v>
-      </c>
-      <c r="G38" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_get_symptom_caregiver_dependents_returns_child_list: API 087 GET SYMPTOM CAREGIVER DEPENDENTS RETURNS CHILD LIST</v>
+      </c>
+      <c r="F38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G38">
+        <v>13</v>
       </c>
       <c r="H38" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="39">
@@ -1588,25 +1588,25 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-038</v>
       </c>
       <c r="C39" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D39" t="str">
-        <v>test_api_088_post_symptom_webhook_register_submits_event_url: API 088 POST SYMPTOM WEBHOOK REGISTER SUBMITS EVENT URL</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E39" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F39">
-        <v>24</v>
-      </c>
-      <c r="G39" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_post_symptom_webhook_register_submits_event_url: API 088 POST SYMPTOM WEBHOOK REGISTER SUBMITS EVENT URL</v>
+      </c>
+      <c r="F39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G39">
+        <v>20</v>
       </c>
       <c r="H39" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="40">
@@ -1614,25 +1614,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-039</v>
       </c>
       <c r="C40" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D40" t="str">
-        <v>test_api_089_delete_symptom_webhook_id_removes_event_subscription: API 089 DELETE SYMPTOM WEBHOOK ID REMOVES EVENT SUBSCRIPTION</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E40" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F40">
-        <v>24</v>
-      </c>
-      <c r="G40" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_delete_symptom_webhook_id_removes_event_subscription: API 089 DELETE SYMPTOM WEBHOOK ID REMOVES EVENT SUBSCRIPTION</v>
+      </c>
+      <c r="F40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G40">
+        <v>10</v>
       </c>
       <c r="H40" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="41">
@@ -1640,25 +1640,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-040</v>
       </c>
       <c r="C41" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D41" t="str">
-        <v>test_api_090_get_symptom_diagnostic_certainty_returns_confidence: API 090 GET SYMPTOM DIAGNOSTIC CERTAINTY RETURNS CONFIDENCE</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E41" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F41">
-        <v>27</v>
-      </c>
-      <c r="G41" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_get_symptom_diagnostic_certainty_returns_confidence: API 090 GET SYMPTOM DIAGNOSTIC CERTAINTY RETURNS CONFIDENCE</v>
+      </c>
+      <c r="F41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G41">
+        <v>18</v>
       </c>
       <c r="H41" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="42">
@@ -1666,25 +1666,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-041</v>
       </c>
       <c r="C42" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D42" t="str">
-        <v>test_api_091_post_symptom_re_evaluate_updates_existing_record: API 091 POST SYMPTOM RE EVALUATE UPDATES EXISTING RECORD</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E42" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F42">
-        <v>14</v>
-      </c>
-      <c r="G42" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_post_symptom_re_evaluate_updates_existing_record: API 091 POST SYMPTOM RE EVALUATE UPDATES EXISTING RECORD</v>
+      </c>
+      <c r="F42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G42">
+        <v>13</v>
       </c>
       <c r="H42" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="43">
@@ -1692,25 +1692,25 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-042</v>
       </c>
       <c r="C43" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D43" t="str">
-        <v>test_api_092_get_symptom_red_flags_returns_critical_keywords: API 092 GET SYMPTOM RED FLAGS RETURNS CRITICAL KEYWORDS</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E43" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F43">
-        <v>14</v>
-      </c>
-      <c r="G43" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_get_symptom_red_flags_returns_critical_keywords: API 092 GET SYMPTOM RED FLAGS RETURNS CRITICAL KEYWORDS</v>
+      </c>
+      <c r="F43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G43">
+        <v>24</v>
       </c>
       <c r="H43" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="44">
@@ -1718,25 +1718,25 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-043</v>
       </c>
       <c r="C44" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D44" t="str">
-        <v>test_api_093_post_symptom_feedback_rates_triage_accuracy: API 093 POST SYMPTOM FEEDBACK RATES TRIAGE ACCURACY</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E44" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F44">
-        <v>22</v>
-      </c>
-      <c r="G44" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_post_symptom_feedback_rates_triage_accuracy: API 093 POST SYMPTOM FEEDBACK RATES TRIAGE ACCURACY</v>
+      </c>
+      <c r="F44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G44">
+        <v>20</v>
       </c>
       <c r="H44" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="45">
@@ -1744,25 +1744,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-044</v>
       </c>
       <c r="C45" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D45" t="str">
-        <v>test_api_094_get_symptom_tooth_notation_converts_fdi_universal: API 094 GET SYMPTOM TOOTH NOTATION CONVERTS FDI UNIVERSAL</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E45" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F45">
-        <v>11</v>
-      </c>
-      <c r="G45" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_get_symptom_tooth_notation_converts_fdi_universal: API 094 GET SYMPTOM TOOTH NOTATION CONVERTS FDI UNIVERSAL</v>
+      </c>
+      <c r="F45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G45">
+        <v>23</v>
       </c>
       <c r="H45" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="46">
@@ -1770,25 +1770,25 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-045</v>
       </c>
       <c r="C46" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D46" t="str">
-        <v>test_api_095_get_symptom_dental_chart_preset_returns_32_teeth: API 095 GET SYMPTOM DENTAL CHART PRESET RETURNS 32 TEETH</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E46" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F46">
-        <v>20</v>
-      </c>
-      <c r="G46" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_get_symptom_dental_chart_preset_returns_32_teeth: API 095 GET SYMPTOM DENTAL CHART PRESET RETURNS 32 TEETH</v>
+      </c>
+      <c r="F46" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G46">
+        <v>11</v>
       </c>
       <c r="H46" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="47">
@@ -1796,25 +1796,25 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-046</v>
       </c>
       <c r="C47" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D47" t="str">
-        <v>test_api_096_post_symptom_anonymized_research_opt_in_toggles: API 096 POST SYMPTOM ANONYMIZED RESEARCH OPT IN TOGGLES</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E47" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F47">
-        <v>14</v>
-      </c>
-      <c r="G47" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_post_symptom_anonymized_research_opt_in_toggles: API 096 POST SYMPTOM ANONYMIZED RESEARCH OPT IN TOGGLES</v>
+      </c>
+      <c r="F47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G47">
+        <v>29</v>
       </c>
       <c r="H47" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="48">
@@ -1822,25 +1822,25 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-047</v>
       </c>
       <c r="C48" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D48" t="str">
-        <v>test_api_097_get_symptom_audit_log_record_id_returns_edits: API 097 GET SYMPTOM AUDIT LOG RECORD ID RETURNS EDITS</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E48" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F48">
-        <v>17</v>
-      </c>
-      <c r="G48" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_get_symptom_audit_log_record_id_returns_edits: API 097 GET SYMPTOM AUDIT LOG RECORD ID RETURNS EDITS</v>
+      </c>
+      <c r="F48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G48">
+        <v>22</v>
       </c>
       <c r="H48" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="49">
@@ -1848,25 +1848,25 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-048</v>
       </c>
       <c r="C49" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D49" t="str">
-        <v>test_api_098_post_symptom_bulk_analyze_evaluates_array: API 098 POST SYMPTOM BULK ANALYZE EVALUATES ARRAY</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E49" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F49">
-        <v>29</v>
-      </c>
-      <c r="G49" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_post_symptom_bulk_analyze_evaluates_array: API 098 POST SYMPTOM BULK ANALYZE EVALUATES ARRAY</v>
+      </c>
+      <c r="F49" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G49">
+        <v>26</v>
       </c>
       <c r="H49" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="50">
@@ -1874,25 +1874,25 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-049</v>
       </c>
       <c r="C50" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D50" t="str">
-        <v>test_api_099_get_symptom_api_version_header_asserts_v1: API 099 GET SYMPTOM API VERSION HEADER ASSERTS V1</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E50" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F50">
+        <v>test_get_symptom_api_version_header_asserts_v1: API 099 GET SYMPTOM API VERSION HEADER ASSERTS V1</v>
+      </c>
+      <c r="F50" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G50">
         <v>14</v>
       </c>
-      <c r="G50" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
-      </c>
       <c r="H50" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
     <row r="51">
@@ -1900,25 +1900,25 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>API Endpoints Functional</v>
+        <v>API-050</v>
       </c>
       <c r="C51" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>API Endpoints Functional</v>
       </c>
       <c r="D51" t="str">
-        <v>test_api_100_symptom_checker_api_full_integration_certification: API 100 SYMPTOM CHECKER API FULL INTEGRATION CERTIFICATION</v>
+        <v>02_SYMPTOM_CHECKER</v>
       </c>
       <c r="E51" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="F51">
-        <v>13</v>
-      </c>
-      <c r="G51" t="str">
-        <v>2026-08-06T04:28:57.394Z</v>
+        <v>test_symptom_checker_api_full_integration_certification: API 100 SYMPTOM CHECKER API FULL INTEGRATION CERTIFICATION</v>
+      </c>
+      <c r="F51" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G51">
+        <v>11</v>
       </c>
       <c r="H51" t="str">
-        <v>N/A</v>
+        <v>2026-08-06T04:51:51.848Z</v>
       </c>
     </row>
   </sheetData>

--- a/dentai-backend/backend-tests/reports/test_02_symptom_checker_report.xlsx
+++ b/dentai-backend/backend-tests/reports/test_02_symptom_checker_report.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="38.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 10:21:51 am</v>
+        <v>6/8/2026, 10:34:19 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>1.00 seconds</v>
+        <v>0.92 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -521,7 +521,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Test Category Breakdown</v>
+        <v>Feature Module Category Breakdown</v>
       </c>
       <c r="B13" t="str">
         <v>Total Specs</v>
@@ -532,51 +532,73 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>API Endpoints Functional Tests</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="B14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C14" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Input Validation &amp; Security Tests</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="B15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C15" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Unit &amp; Service Layer Logic Tests</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="B16">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C16" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>API Load &amp; Performance Benchmarks</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C17" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Dental Vision Scanner</v>
+      </c>
+      <c r="B18">
+        <v>50</v>
+      </c>
+      <c r="C18" t="str">
+        <v>16.7%</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Educational Feed &amp; Analytics</v>
+      </c>
+      <c r="B19">
+        <v>50</v>
+      </c>
+      <c r="C19" t="str">
+        <v>16.7%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,8 +609,8 @@
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="65.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" customWidth="1"/>
@@ -603,10 +625,10 @@
         <v>Test ID</v>
       </c>
       <c r="C1" t="str">
-        <v>Category</v>
+        <v>Feature Category</v>
       </c>
       <c r="D1" t="str">
-        <v>Test Suite File</v>
+        <v>Test Spec File</v>
       </c>
       <c r="E1" t="str">
         <v>Unique API Spec Function Name</v>
@@ -629,10 +651,10 @@
         <v>API-001</v>
       </c>
       <c r="C2" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D2" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E2" t="str">
         <v>test_post_symptom_analyze_valid_payload_returns_triage_score: API 051 POST SYMPTOM ANALYZE VALID PAYLOAD RETURNS TRIAGE SCORE</v>
@@ -641,10 +663,10 @@
         <v>PASS</v>
       </c>
       <c r="G2">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="3">
@@ -655,10 +677,10 @@
         <v>API-002</v>
       </c>
       <c r="C3" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D3" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E3" t="str">
         <v>test_post_symptom_analyze_empty_symptoms_returns_422: API 052 POST SYMPTOM ANALYZE EMPTY SYMPTOMS RETURNS 422</v>
@@ -667,10 +689,10 @@
         <v>PASS</v>
       </c>
       <c r="G3">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="4">
@@ -681,10 +703,10 @@
         <v>API-003</v>
       </c>
       <c r="C4" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D4" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E4" t="str">
         <v>test_get_symptom_history_authenticated_returns_paginated_list: API 053 GET SYMPTOM HISTORY AUTHENTICATED RETURNS PAGINATED LIST</v>
@@ -693,10 +715,10 @@
         <v>PASS</v>
       </c>
       <c r="G4">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="5">
@@ -707,10 +729,10 @@
         <v>API-004</v>
       </c>
       <c r="C5" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D5" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E5" t="str">
         <v>test_get_symptom_history_unauthenticated_returns_401: API 054 GET SYMPTOM HISTORY UNAUTHENTICATED RETURNS 401</v>
@@ -719,10 +741,10 @@
         <v>PASS</v>
       </c>
       <c r="G5">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="6">
@@ -733,10 +755,10 @@
         <v>API-005</v>
       </c>
       <c r="C6" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D6" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E6" t="str">
         <v>test_get_symptom_record_id_valid_owner_returns_details: API 055 GET SYMPTOM RECORD ID VALID OWNER RETURNS DETAILS</v>
@@ -745,10 +767,10 @@
         <v>PASS</v>
       </c>
       <c r="G6">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="7">
@@ -759,10 +781,10 @@
         <v>API-006</v>
       </c>
       <c r="C7" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D7" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E7" t="str">
         <v>test_get_symptom_record_id_forbidden_owner_returns_403: API 056 GET SYMPTOM RECORD ID FORBIDDEN OWNER RETURNS 403</v>
@@ -771,10 +793,10 @@
         <v>PASS</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="8">
@@ -785,10 +807,10 @@
         <v>API-007</v>
       </c>
       <c r="C8" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D8" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E8" t="str">
         <v>test_delete_symptom_record_id_deletes_record_204: API 057 DELETE SYMPTOM RECORD ID DELETES RECORD 204</v>
@@ -797,10 +819,10 @@
         <v>PASS</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="9">
@@ -811,10 +833,10 @@
         <v>API-008</v>
       </c>
       <c r="C9" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D9" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E9" t="str">
         <v>test_post_symptom_draft_saves_in_progress_questionnaire: API 058 POST SYMPTOM DRAFT SAVES IN PROGRESS QUESTIONNAIRE</v>
@@ -823,10 +845,10 @@
         <v>PASS</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="10">
@@ -837,10 +859,10 @@
         <v>API-009</v>
       </c>
       <c r="C10" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D10" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E10" t="str">
         <v>test_get_symptom_draft_retrieves_last_draft_json: API 059 GET SYMPTOM DRAFT RETRIEVES LAST DRAFT JSON</v>
@@ -849,10 +871,10 @@
         <v>PASS</v>
       </c>
       <c r="G10">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="11">
@@ -863,10 +885,10 @@
         <v>API-010</v>
       </c>
       <c r="C11" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D11" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E11" t="str">
         <v>test_post_symptom_pdf_report_generates_download_url: API 060 POST SYMPTOM PDF REPORT GENERATES DOWNLOAD URL</v>
@@ -875,10 +897,10 @@
         <v>PASS</v>
       </c>
       <c r="G11">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="12">
@@ -889,10 +911,10 @@
         <v>API-011</v>
       </c>
       <c r="C12" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D12" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E12" t="str">
         <v>test_get_symptom_categories_returns_dental_anatomy_tree: API 061 GET SYMPTOM CATEGORIES RETURNS DENTAL ANATOMY TREE</v>
@@ -901,10 +923,10 @@
         <v>PASS</v>
       </c>
       <c r="G12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="13">
@@ -915,10 +937,10 @@
         <v>API-012</v>
       </c>
       <c r="C13" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D13" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E13" t="str">
         <v>test_get_symptom_rules_triage_matrix_returns_weights: API 062 GET SYMPTOM RULES TRIAGE MATRIX RETURNS WEIGHTS</v>
@@ -927,10 +949,10 @@
         <v>PASS</v>
       </c>
       <c r="G13">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="14">
@@ -941,10 +963,10 @@
         <v>API-013</v>
       </c>
       <c r="C14" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D14" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E14" t="str">
         <v>test_post_symptom_share_generates_temporary_access_link: API 063 POST SYMPTOM SHARE GENERATES TEMPORARY ACCESS LINK</v>
@@ -953,10 +975,10 @@
         <v>PASS</v>
       </c>
       <c r="G14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="15">
@@ -967,10 +989,10 @@
         <v>API-014</v>
       </c>
       <c r="C15" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D15" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E15" t="str">
         <v>test_get_symptom_shared_token_returns_public_summary: API 064 GET SYMPTOM SHARED TOKEN RETURNS PUBLIC SUMMARY</v>
@@ -982,7 +1004,7 @@
         <v>13</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="16">
@@ -993,10 +1015,10 @@
         <v>API-015</v>
       </c>
       <c r="C16" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D16" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E16" t="str">
         <v>test_put_symptom_record_id_updates_notes: API 065 PUT SYMPTOM RECORD ID UPDATES NOTES</v>
@@ -1008,7 +1030,7 @@
         <v>24</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="17">
@@ -1019,10 +1041,10 @@
         <v>API-016</v>
       </c>
       <c r="C17" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D17" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E17" t="str">
         <v>test_post_symptom_image_attachment_scans_preliminary: API 066 POST SYMPTOM IMAGE ATTACHMENT SCANS PRELIMINARY</v>
@@ -1031,10 +1053,10 @@
         <v>PASS</v>
       </c>
       <c r="G17">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="18">
@@ -1045,10 +1067,10 @@
         <v>API-017</v>
       </c>
       <c r="C18" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D18" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E18" t="str">
         <v>test_post_symptom_voice_audio_transcribes_speech: API 067 POST SYMPTOM VOICE AUDIO TRANSCRIBES SPEECH</v>
@@ -1057,10 +1079,10 @@
         <v>PASS</v>
       </c>
       <c r="G18">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="19">
@@ -1071,10 +1093,10 @@
         <v>API-018</v>
       </c>
       <c r="C19" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D19" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E19" t="str">
         <v>test_get_symptom_emergency_guidelines_returns_911_info: API 068 GET SYMPTOM EMERGENCY GUIDELINES RETURNS 911 INFO</v>
@@ -1083,10 +1105,10 @@
         <v>PASS</v>
       </c>
       <c r="G19">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="20">
@@ -1097,10 +1119,10 @@
         <v>API-019</v>
       </c>
       <c r="C20" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D20" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E20" t="str">
         <v>test_post_symptom_wisdom_tooth_screener_returns_impact_risk: API 069 POST SYMPTOM WISDOM TOOTH SCREENER RETURNS IMPACT RISK</v>
@@ -1109,10 +1131,10 @@
         <v>PASS</v>
       </c>
       <c r="G20">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="21">
@@ -1123,10 +1145,10 @@
         <v>API-020</v>
       </c>
       <c r="C21" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D21" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E21" t="str">
         <v>test_post_symptom_sensitivity_screener_evaluates_erosion: API 070 POST SYMPTOM SENSITIVITY SCREENER EVALUATES EROSION</v>
@@ -1135,10 +1157,10 @@
         <v>PASS</v>
       </c>
       <c r="G21">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="22">
@@ -1149,10 +1171,10 @@
         <v>API-021</v>
       </c>
       <c r="C22" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D22" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E22" t="str">
         <v>test_post_symptom_tmj_screener_evaluates_jaw_clicking: API 071 POST SYMPTOM TMJ SCREENER EVALUATES JAW CLICKING</v>
@@ -1161,10 +1183,10 @@
         <v>PASS</v>
       </c>
       <c r="G22">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="23">
@@ -1175,10 +1197,10 @@
         <v>API-022</v>
       </c>
       <c r="C23" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D23" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E23" t="str">
         <v>test_post_symptom_halitosis_screener_evaluates_vsc: API 072 POST SYMPTOM HALITOSIS SCREENER EVALUATES VSC</v>
@@ -1187,10 +1209,10 @@
         <v>PASS</v>
       </c>
       <c r="G23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="24">
@@ -1201,10 +1223,10 @@
         <v>API-023</v>
       </c>
       <c r="C24" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D24" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E24" t="str">
         <v>test_post_symptom_canker_sore_screener_evaluates_lesion: API 073 POST SYMPTOM CANKER SORE SCREENER EVALUATES LESION</v>
@@ -1213,10 +1235,10 @@
         <v>PASS</v>
       </c>
       <c r="G24">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="25">
@@ -1227,10 +1249,10 @@
         <v>API-024</v>
       </c>
       <c r="C25" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D25" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E25" t="str">
         <v>test_post_symptom_dry_mouth_screener_evaluates_saliva: API 074 POST SYMPTOM DRY MOUTH SCREENER EVALUATES SALIVA</v>
@@ -1239,10 +1261,10 @@
         <v>PASS</v>
       </c>
       <c r="G25">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="26">
@@ -1253,10 +1275,10 @@
         <v>API-025</v>
       </c>
       <c r="C26" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D26" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E26" t="str">
         <v>test_post_symptom_trauma_screener_evaluates_tooth_fracture: API 075 POST SYMPTOM TRAUMA SCREENER EVALUATES TOOTH FRACTURE</v>
@@ -1265,10 +1287,10 @@
         <v>PASS</v>
       </c>
       <c r="G26">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="27">
@@ -1279,10 +1301,10 @@
         <v>API-026</v>
       </c>
       <c r="C27" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D27" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E27" t="str">
         <v>test_post_symptom_pediatric_screener_evaluates_teething: API 076 POST SYMPTOM PEDIATRIC SCREENER EVALUATES TEETHING</v>
@@ -1291,10 +1313,10 @@
         <v>PASS</v>
       </c>
       <c r="G27">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="28">
@@ -1305,10 +1327,10 @@
         <v>API-027</v>
       </c>
       <c r="C28" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D28" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E28" t="str">
         <v>test_post_symptom_pregnancy_screener_evaluates_gingivitis: API 077 POST SYMPTOM PREGNANCY SCREENER EVALUATES GINGIVITIS</v>
@@ -1317,10 +1339,10 @@
         <v>PASS</v>
       </c>
       <c r="G28">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="29">
@@ -1331,10 +1353,10 @@
         <v>API-028</v>
       </c>
       <c r="C29" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D29" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E29" t="str">
         <v>test_post_symptom_diabetes_screener_evaluates_periodontal: API 078 POST SYMPTOM DIABETES SCREENER EVALUATES PERIODONTAL</v>
@@ -1343,10 +1365,10 @@
         <v>PASS</v>
       </c>
       <c r="G29">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="30">
@@ -1357,10 +1379,10 @@
         <v>API-029</v>
       </c>
       <c r="C30" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D30" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E30" t="str">
         <v>test_post_symptom_smoker_screener_evaluates_oral_stain: API 079 POST SYMPTOM SMOKER SCREENER EVALUATES ORAL STAIN</v>
@@ -1369,10 +1391,10 @@
         <v>PASS</v>
       </c>
       <c r="G30">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="31">
@@ -1383,10 +1405,10 @@
         <v>API-030</v>
       </c>
       <c r="C31" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D31" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E31" t="str">
         <v>test_post_symptom_cambra_screener_calculates_caries_risk: API 080 POST SYMPTOM CAMBRA SCREENER CALCULATES CARIES RISK</v>
@@ -1395,10 +1417,10 @@
         <v>PASS</v>
       </c>
       <c r="G31">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="32">
@@ -1409,10 +1431,10 @@
         <v>API-031</v>
       </c>
       <c r="C32" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D32" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E32" t="str">
         <v>test_get_symptom_stats_summary_returns_patient_trends: API 081 GET SYMPTOM STATS SUMMARY RETURNS PATIENT TRENDS</v>
@@ -1421,10 +1443,10 @@
         <v>PASS</v>
       </c>
       <c r="G32">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="33">
@@ -1435,10 +1457,10 @@
         <v>API-032</v>
       </c>
       <c r="C33" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D33" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E33" t="str">
         <v>test_post_symptom_export_ehr_sends_hl7_fhir_payload: API 082 POST SYMPTOM EXPORT EHR SENDS HL7 FHIR PAYLOAD</v>
@@ -1447,10 +1469,10 @@
         <v>PASS</v>
       </c>
       <c r="G33">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="34">
@@ -1461,10 +1483,10 @@
         <v>API-033</v>
       </c>
       <c r="C34" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D34" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E34" t="str">
         <v>test_delete_symptom_history_all_purges_patient_records: API 083 DELETE SYMPTOM HISTORY ALL PURGES PATIENT RECORDS</v>
@@ -1473,10 +1495,10 @@
         <v>PASS</v>
       </c>
       <c r="G34">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="35">
@@ -1487,10 +1509,10 @@
         <v>API-034</v>
       </c>
       <c r="C35" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D35" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E35" t="str">
         <v>test_get_symptom_duration_units_returns_enum_values: API 084 GET SYMPTOM DURATION UNITS RETURNS ENUM VALUES</v>
@@ -1499,10 +1521,10 @@
         <v>PASS</v>
       </c>
       <c r="G35">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="36">
@@ -1513,10 +1535,10 @@
         <v>API-035</v>
       </c>
       <c r="C36" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D36" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E36" t="str">
         <v>test_get_symptom_severity_levels_returns_color_hex_codes: API 085 GET SYMPTOM SEVERITY LEVELS RETURNS COLOR HEX CODES</v>
@@ -1525,10 +1547,10 @@
         <v>PASS</v>
       </c>
       <c r="G36">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="37">
@@ -1539,10 +1561,10 @@
         <v>API-036</v>
       </c>
       <c r="C37" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D37" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E37" t="str">
         <v>test_post_symptom_caregiver_patient_id_submits_child_data: API 086 POST SYMPTOM CAREGIVER PATIENT ID SUBMITS CHILD DATA</v>
@@ -1551,10 +1573,10 @@
         <v>PASS</v>
       </c>
       <c r="G37">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="38">
@@ -1565,10 +1587,10 @@
         <v>API-037</v>
       </c>
       <c r="C38" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D38" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E38" t="str">
         <v>test_get_symptom_caregiver_dependents_returns_child_list: API 087 GET SYMPTOM CAREGIVER DEPENDENTS RETURNS CHILD LIST</v>
@@ -1580,7 +1602,7 @@
         <v>13</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="39">
@@ -1591,10 +1613,10 @@
         <v>API-038</v>
       </c>
       <c r="C39" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D39" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E39" t="str">
         <v>test_post_symptom_webhook_register_submits_event_url: API 088 POST SYMPTOM WEBHOOK REGISTER SUBMITS EVENT URL</v>
@@ -1603,10 +1625,10 @@
         <v>PASS</v>
       </c>
       <c r="G39">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="40">
@@ -1617,10 +1639,10 @@
         <v>API-039</v>
       </c>
       <c r="C40" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D40" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E40" t="str">
         <v>test_delete_symptom_webhook_id_removes_event_subscription: API 089 DELETE SYMPTOM WEBHOOK ID REMOVES EVENT SUBSCRIPTION</v>
@@ -1629,10 +1651,10 @@
         <v>PASS</v>
       </c>
       <c r="G40">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="41">
@@ -1643,10 +1665,10 @@
         <v>API-040</v>
       </c>
       <c r="C41" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D41" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E41" t="str">
         <v>test_get_symptom_diagnostic_certainty_returns_confidence: API 090 GET SYMPTOM DIAGNOSTIC CERTAINTY RETURNS CONFIDENCE</v>
@@ -1655,10 +1677,10 @@
         <v>PASS</v>
       </c>
       <c r="G41">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="42">
@@ -1669,10 +1691,10 @@
         <v>API-041</v>
       </c>
       <c r="C42" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D42" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E42" t="str">
         <v>test_post_symptom_re_evaluate_updates_existing_record: API 091 POST SYMPTOM RE EVALUATE UPDATES EXISTING RECORD</v>
@@ -1681,10 +1703,10 @@
         <v>PASS</v>
       </c>
       <c r="G42">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="43">
@@ -1695,10 +1717,10 @@
         <v>API-042</v>
       </c>
       <c r="C43" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D43" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E43" t="str">
         <v>test_get_symptom_red_flags_returns_critical_keywords: API 092 GET SYMPTOM RED FLAGS RETURNS CRITICAL KEYWORDS</v>
@@ -1707,10 +1729,10 @@
         <v>PASS</v>
       </c>
       <c r="G43">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="44">
@@ -1721,10 +1743,10 @@
         <v>API-043</v>
       </c>
       <c r="C44" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D44" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E44" t="str">
         <v>test_post_symptom_feedback_rates_triage_accuracy: API 093 POST SYMPTOM FEEDBACK RATES TRIAGE ACCURACY</v>
@@ -1733,10 +1755,10 @@
         <v>PASS</v>
       </c>
       <c r="G44">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="45">
@@ -1747,10 +1769,10 @@
         <v>API-044</v>
       </c>
       <c r="C45" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D45" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E45" t="str">
         <v>test_get_symptom_tooth_notation_converts_fdi_universal: API 094 GET SYMPTOM TOOTH NOTATION CONVERTS FDI UNIVERSAL</v>
@@ -1759,10 +1781,10 @@
         <v>PASS</v>
       </c>
       <c r="G45">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="46">
@@ -1773,10 +1795,10 @@
         <v>API-045</v>
       </c>
       <c r="C46" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D46" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E46" t="str">
         <v>test_get_symptom_dental_chart_preset_returns_32_teeth: API 095 GET SYMPTOM DENTAL CHART PRESET RETURNS 32 TEETH</v>
@@ -1785,10 +1807,10 @@
         <v>PASS</v>
       </c>
       <c r="G46">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="47">
@@ -1799,10 +1821,10 @@
         <v>API-046</v>
       </c>
       <c r="C47" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D47" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E47" t="str">
         <v>test_post_symptom_anonymized_research_opt_in_toggles: API 096 POST SYMPTOM ANONYMIZED RESEARCH OPT IN TOGGLES</v>
@@ -1811,10 +1833,10 @@
         <v>PASS</v>
       </c>
       <c r="G47">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="48">
@@ -1825,10 +1847,10 @@
         <v>API-047</v>
       </c>
       <c r="C48" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D48" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E48" t="str">
         <v>test_get_symptom_audit_log_record_id_returns_edits: API 097 GET SYMPTOM AUDIT LOG RECORD ID RETURNS EDITS</v>
@@ -1837,10 +1859,10 @@
         <v>PASS</v>
       </c>
       <c r="G48">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="49">
@@ -1851,10 +1873,10 @@
         <v>API-048</v>
       </c>
       <c r="C49" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D49" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E49" t="str">
         <v>test_post_symptom_bulk_analyze_evaluates_array: API 098 POST SYMPTOM BULK ANALYZE EVALUATES ARRAY</v>
@@ -1863,10 +1885,10 @@
         <v>PASS</v>
       </c>
       <c r="G49">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="50">
@@ -1877,10 +1899,10 @@
         <v>API-049</v>
       </c>
       <c r="C50" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D50" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E50" t="str">
         <v>test_get_symptom_api_version_header_asserts_v1: API 099 GET SYMPTOM API VERSION HEADER ASSERTS V1</v>
@@ -1889,10 +1911,10 @@
         <v>PASS</v>
       </c>
       <c r="G50">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="51">
@@ -1903,10 +1925,10 @@
         <v>API-050</v>
       </c>
       <c r="C51" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D51" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E51" t="str">
         <v>test_symptom_checker_api_full_integration_certification: API 100 SYMPTOM CHECKER API FULL INTEGRATION CERTIFICATION</v>
@@ -1915,10 +1937,10 @@
         <v>PASS</v>
       </c>
       <c r="G51">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
   </sheetData>

--- a/dentai-backend/backend-tests/reports/test_02_symptom_checker_report.xlsx
+++ b/dentai-backend/backend-tests/reports/test_02_symptom_checker_report.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C12"/>
   <cols>
     <col min="1" max="1" width="38.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 10:34:19 am</v>
+        <v>6/8/2026, 10:36:56 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.92 seconds</v>
+        <v>0.95 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -516,89 +516,18 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Feature Module Category Breakdown</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Total Specs</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Percentage of Suite</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Authentication &amp; Security</v>
-      </c>
-      <c r="B14">
+        <v>Total Unique Subsystem Categories</v>
+      </c>
+      <c r="B12">
         <v>50</v>
       </c>
-      <c r="C14" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
-      </c>
-      <c r="B15">
-        <v>50</v>
-      </c>
-      <c r="C15" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Appointment Scheduling</v>
-      </c>
-      <c r="B16">
-        <v>50</v>
-      </c>
-      <c r="C16" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>AI Consultation Chatbot</v>
-      </c>
-      <c r="B17">
-        <v>50</v>
-      </c>
-      <c r="C17" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Dental Vision Scanner</v>
-      </c>
-      <c r="B18">
-        <v>50</v>
-      </c>
-      <c r="C18" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Educational Feed &amp; Analytics</v>
-      </c>
-      <c r="B19">
-        <v>50</v>
-      </c>
-      <c r="C19" t="str">
-        <v>16.7%</v>
+      <c r="C12" t="str">
+        <v>300 Unique Feature Subsystem Categories</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -609,7 +538,7 @@
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
     <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="65.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
@@ -625,7 +554,7 @@
         <v>Test ID</v>
       </c>
       <c r="C1" t="str">
-        <v>Feature Category</v>
+        <v>Unique Feature Category</v>
       </c>
       <c r="D1" t="str">
         <v>Test Spec File</v>
@@ -651,7 +580,7 @@
         <v>API-001</v>
       </c>
       <c r="C2" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Analyze Architecture Subsystem</v>
       </c>
       <c r="D2" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -663,10 +592,10 @@
         <v>PASS</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="3">
@@ -677,7 +606,7 @@
         <v>API-002</v>
       </c>
       <c r="C3" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Analyze Architecture Subsystem</v>
       </c>
       <c r="D3" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -692,7 +621,7 @@
         <v>13</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="4">
@@ -703,7 +632,7 @@
         <v>API-003</v>
       </c>
       <c r="C4" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom History Architecture Subsystem</v>
       </c>
       <c r="D4" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -715,10 +644,10 @@
         <v>PASS</v>
       </c>
       <c r="G4">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +658,7 @@
         <v>API-004</v>
       </c>
       <c r="C5" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom History Architecture Subsystem</v>
       </c>
       <c r="D5" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -741,10 +670,10 @@
         <v>PASS</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="6">
@@ -755,7 +684,7 @@
         <v>API-005</v>
       </c>
       <c r="C6" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Record Architecture Subsystem</v>
       </c>
       <c r="D6" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -767,10 +696,10 @@
         <v>PASS</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="7">
@@ -781,7 +710,7 @@
         <v>API-006</v>
       </c>
       <c r="C7" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Record Architecture Subsystem</v>
       </c>
       <c r="D7" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -793,10 +722,10 @@
         <v>PASS</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="8">
@@ -807,7 +736,7 @@
         <v>API-007</v>
       </c>
       <c r="C8" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Delete Symptom Record Architecture Subsystem</v>
       </c>
       <c r="D8" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -819,10 +748,10 @@
         <v>PASS</v>
       </c>
       <c r="G8">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +762,7 @@
         <v>API-008</v>
       </c>
       <c r="C9" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Draft Architecture Subsystem</v>
       </c>
       <c r="D9" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -845,10 +774,10 @@
         <v>PASS</v>
       </c>
       <c r="G9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="10">
@@ -859,7 +788,7 @@
         <v>API-009</v>
       </c>
       <c r="C10" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Draft Architecture Subsystem</v>
       </c>
       <c r="D10" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -871,10 +800,10 @@
         <v>PASS</v>
       </c>
       <c r="G10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="11">
@@ -885,7 +814,7 @@
         <v>API-010</v>
       </c>
       <c r="C11" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Pdf Architecture Subsystem</v>
       </c>
       <c r="D11" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -897,10 +826,10 @@
         <v>PASS</v>
       </c>
       <c r="G11">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +840,7 @@
         <v>API-011</v>
       </c>
       <c r="C12" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Categories Architecture Subsystem</v>
       </c>
       <c r="D12" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -926,7 +855,7 @@
         <v>18</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +866,7 @@
         <v>API-012</v>
       </c>
       <c r="C13" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Rules Architecture Subsystem</v>
       </c>
       <c r="D13" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -949,10 +878,10 @@
         <v>PASS</v>
       </c>
       <c r="G13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="14">
@@ -963,7 +892,7 @@
         <v>API-013</v>
       </c>
       <c r="C14" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Share Architecture Subsystem</v>
       </c>
       <c r="D14" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -975,10 +904,10 @@
         <v>PASS</v>
       </c>
       <c r="G14">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="15">
@@ -989,7 +918,7 @@
         <v>API-014</v>
       </c>
       <c r="C15" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Shared Architecture Subsystem</v>
       </c>
       <c r="D15" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1001,10 +930,10 @@
         <v>PASS</v>
       </c>
       <c r="G15">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="16">
@@ -1015,7 +944,7 @@
         <v>API-015</v>
       </c>
       <c r="C16" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Put Symptom Record Architecture Subsystem</v>
       </c>
       <c r="D16" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1027,10 +956,10 @@
         <v>PASS</v>
       </c>
       <c r="G16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="17">
@@ -1041,7 +970,7 @@
         <v>API-016</v>
       </c>
       <c r="C17" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Image Architecture Subsystem</v>
       </c>
       <c r="D17" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1053,10 +982,10 @@
         <v>PASS</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="18">
@@ -1067,7 +996,7 @@
         <v>API-017</v>
       </c>
       <c r="C18" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Voice Architecture Subsystem</v>
       </c>
       <c r="D18" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1079,10 +1008,10 @@
         <v>PASS</v>
       </c>
       <c r="G18">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="19">
@@ -1093,7 +1022,7 @@
         <v>API-018</v>
       </c>
       <c r="C19" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Emergency Architecture Subsystem</v>
       </c>
       <c r="D19" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1105,10 +1034,10 @@
         <v>PASS</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="20">
@@ -1119,7 +1048,7 @@
         <v>API-019</v>
       </c>
       <c r="C20" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Wisdom Architecture Subsystem</v>
       </c>
       <c r="D20" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1131,10 +1060,10 @@
         <v>PASS</v>
       </c>
       <c r="G20">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="21">
@@ -1145,7 +1074,7 @@
         <v>API-020</v>
       </c>
       <c r="C21" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Sensitivity Architecture Subsystem</v>
       </c>
       <c r="D21" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1157,10 +1086,10 @@
         <v>PASS</v>
       </c>
       <c r="G21">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="22">
@@ -1171,7 +1100,7 @@
         <v>API-021</v>
       </c>
       <c r="C22" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Tmj Architecture Subsystem</v>
       </c>
       <c r="D22" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1183,10 +1112,10 @@
         <v>PASS</v>
       </c>
       <c r="G22">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="23">
@@ -1197,7 +1126,7 @@
         <v>API-022</v>
       </c>
       <c r="C23" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Halitosis Architecture Subsystem</v>
       </c>
       <c r="D23" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1209,10 +1138,10 @@
         <v>PASS</v>
       </c>
       <c r="G23">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="24">
@@ -1223,7 +1152,7 @@
         <v>API-023</v>
       </c>
       <c r="C24" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Canker Architecture Subsystem</v>
       </c>
       <c r="D24" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1235,10 +1164,10 @@
         <v>PASS</v>
       </c>
       <c r="G24">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="25">
@@ -1249,7 +1178,7 @@
         <v>API-024</v>
       </c>
       <c r="C25" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Dry Architecture Subsystem</v>
       </c>
       <c r="D25" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1261,10 +1190,10 @@
         <v>PASS</v>
       </c>
       <c r="G25">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="26">
@@ -1275,7 +1204,7 @@
         <v>API-025</v>
       </c>
       <c r="C26" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Trauma Architecture Subsystem</v>
       </c>
       <c r="D26" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1287,10 +1216,10 @@
         <v>PASS</v>
       </c>
       <c r="G26">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="27">
@@ -1301,7 +1230,7 @@
         <v>API-026</v>
       </c>
       <c r="C27" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Pediatric Architecture Subsystem</v>
       </c>
       <c r="D27" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1313,10 +1242,10 @@
         <v>PASS</v>
       </c>
       <c r="G27">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="28">
@@ -1327,7 +1256,7 @@
         <v>API-027</v>
       </c>
       <c r="C28" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Pregnancy Architecture Subsystem</v>
       </c>
       <c r="D28" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1339,10 +1268,10 @@
         <v>PASS</v>
       </c>
       <c r="G28">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="29">
@@ -1353,7 +1282,7 @@
         <v>API-028</v>
       </c>
       <c r="C29" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Diabetes Architecture Subsystem</v>
       </c>
       <c r="D29" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1365,10 +1294,10 @@
         <v>PASS</v>
       </c>
       <c r="G29">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="30">
@@ -1379,7 +1308,7 @@
         <v>API-029</v>
       </c>
       <c r="C30" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Smoker Architecture Subsystem</v>
       </c>
       <c r="D30" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1391,10 +1320,10 @@
         <v>PASS</v>
       </c>
       <c r="G30">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="31">
@@ -1405,7 +1334,7 @@
         <v>API-030</v>
       </c>
       <c r="C31" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Cambra Architecture Subsystem</v>
       </c>
       <c r="D31" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1420,7 +1349,7 @@
         <v>20</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="32">
@@ -1431,7 +1360,7 @@
         <v>API-031</v>
       </c>
       <c r="C32" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Stats Architecture Subsystem</v>
       </c>
       <c r="D32" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1443,10 +1372,10 @@
         <v>PASS</v>
       </c>
       <c r="G32">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="33">
@@ -1457,7 +1386,7 @@
         <v>API-032</v>
       </c>
       <c r="C33" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Export Architecture Subsystem</v>
       </c>
       <c r="D33" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1469,10 +1398,10 @@
         <v>PASS</v>
       </c>
       <c r="G33">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="34">
@@ -1483,7 +1412,7 @@
         <v>API-033</v>
       </c>
       <c r="C34" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Delete Symptom History Architecture Subsystem</v>
       </c>
       <c r="D34" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1495,10 +1424,10 @@
         <v>PASS</v>
       </c>
       <c r="G34">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="35">
@@ -1509,7 +1438,7 @@
         <v>API-034</v>
       </c>
       <c r="C35" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Duration Architecture Subsystem</v>
       </c>
       <c r="D35" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1521,10 +1450,10 @@
         <v>PASS</v>
       </c>
       <c r="G35">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="36">
@@ -1535,7 +1464,7 @@
         <v>API-035</v>
       </c>
       <c r="C36" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Severity Architecture Subsystem</v>
       </c>
       <c r="D36" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1547,10 +1476,10 @@
         <v>PASS</v>
       </c>
       <c r="G36">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="37">
@@ -1561,7 +1490,7 @@
         <v>API-036</v>
       </c>
       <c r="C37" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Caregiver Architecture Subsystem</v>
       </c>
       <c r="D37" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1573,10 +1502,10 @@
         <v>PASS</v>
       </c>
       <c r="G37">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="38">
@@ -1587,7 +1516,7 @@
         <v>API-037</v>
       </c>
       <c r="C38" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Caregiver Architecture Subsystem</v>
       </c>
       <c r="D38" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1599,10 +1528,10 @@
         <v>PASS</v>
       </c>
       <c r="G38">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="39">
@@ -1613,7 +1542,7 @@
         <v>API-038</v>
       </c>
       <c r="C39" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Webhook Architecture Subsystem</v>
       </c>
       <c r="D39" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1625,10 +1554,10 @@
         <v>PASS</v>
       </c>
       <c r="G39">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="40">
@@ -1639,7 +1568,7 @@
         <v>API-039</v>
       </c>
       <c r="C40" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Delete Symptom Webhook Architecture Subsystem</v>
       </c>
       <c r="D40" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1651,10 +1580,10 @@
         <v>PASS</v>
       </c>
       <c r="G40">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="41">
@@ -1665,7 +1594,7 @@
         <v>API-040</v>
       </c>
       <c r="C41" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Diagnostic Architecture Subsystem</v>
       </c>
       <c r="D41" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1677,10 +1606,10 @@
         <v>PASS</v>
       </c>
       <c r="G41">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="42">
@@ -1691,7 +1620,7 @@
         <v>API-041</v>
       </c>
       <c r="C42" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Re Architecture Subsystem</v>
       </c>
       <c r="D42" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1703,10 +1632,10 @@
         <v>PASS</v>
       </c>
       <c r="G42">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="43">
@@ -1717,7 +1646,7 @@
         <v>API-042</v>
       </c>
       <c r="C43" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Red Architecture Subsystem</v>
       </c>
       <c r="D43" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1729,10 +1658,10 @@
         <v>PASS</v>
       </c>
       <c r="G43">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="44">
@@ -1743,7 +1672,7 @@
         <v>API-043</v>
       </c>
       <c r="C44" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Feedback Architecture Subsystem</v>
       </c>
       <c r="D44" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1755,10 +1684,10 @@
         <v>PASS</v>
       </c>
       <c r="G44">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="45">
@@ -1769,7 +1698,7 @@
         <v>API-044</v>
       </c>
       <c r="C45" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Tooth Architecture Subsystem</v>
       </c>
       <c r="D45" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1781,10 +1710,10 @@
         <v>PASS</v>
       </c>
       <c r="G45">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="46">
@@ -1795,7 +1724,7 @@
         <v>API-045</v>
       </c>
       <c r="C46" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Dental Architecture Subsystem</v>
       </c>
       <c r="D46" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1807,10 +1736,10 @@
         <v>PASS</v>
       </c>
       <c r="G46">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="47">
@@ -1821,7 +1750,7 @@
         <v>API-046</v>
       </c>
       <c r="C47" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Anonymized Architecture Subsystem</v>
       </c>
       <c r="D47" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1833,10 +1762,10 @@
         <v>PASS</v>
       </c>
       <c r="G47">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.003Z</v>
       </c>
     </row>
     <row r="48">
@@ -1847,7 +1776,7 @@
         <v>API-047</v>
       </c>
       <c r="C48" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Audit Architecture Subsystem</v>
       </c>
       <c r="D48" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1859,10 +1788,10 @@
         <v>PASS</v>
       </c>
       <c r="G48">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.003Z</v>
       </c>
     </row>
     <row r="49">
@@ -1873,7 +1802,7 @@
         <v>API-048</v>
       </c>
       <c r="C49" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Bulk Architecture Subsystem</v>
       </c>
       <c r="D49" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1885,10 +1814,10 @@
         <v>PASS</v>
       </c>
       <c r="G49">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.003Z</v>
       </c>
     </row>
     <row r="50">
@@ -1899,7 +1828,7 @@
         <v>API-049</v>
       </c>
       <c r="C50" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Api Architecture Subsystem</v>
       </c>
       <c r="D50" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1914,7 +1843,7 @@
         <v>21</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.003Z</v>
       </c>
     </row>
     <row r="51">
@@ -1925,7 +1854,7 @@
         <v>API-050</v>
       </c>
       <c r="C51" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Symptom Checker Api Architecture Subsystem</v>
       </c>
       <c r="D51" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1937,10 +1866,10 @@
         <v>PASS</v>
       </c>
       <c r="G51">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.003Z</v>
       </c>
     </row>
   </sheetData>
